--- a/data/trans_orig/IP07KS_C07_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C07_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de trato justo por parte de sus padres en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de trato justo por parte de sus padres, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>65770</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>56119</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>74049</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>75,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40828</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>33698</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47554</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60,11%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>49,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>67835</t>
+          <t>42944</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59175</t>
+          <t>36048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75531</t>
+          <t>50438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>108662</t>
+          <t>108714</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97142</t>
+          <t>96494</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120061</t>
+          <t>120387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28606</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20905</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37268</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>23613</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17250</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30849</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27215</t>
+          <t>25319</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>50828</t>
+          <t>53925</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41048</t>
+          <t>42879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62362</t>
+          <t>66188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5994</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3047</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1126</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4122</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4026</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3522</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>937</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>363</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79143</t>
+          <t>107948</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45399</t>
+          <t>92698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100523</t>
+          <t>121845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>110133</t>
+          <t>82667</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95656</t>
+          <t>71608</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128181</t>
+          <t>92674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>189277</t>
+          <t>190614</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140832</t>
+          <t>173196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215217</t>
+          <t>208151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>70,09%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50169</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>37528</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>65744</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,34%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>38,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>59329</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>37179</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>94935</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>41,62%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,08%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49485</t>
+          <t>38448</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34329</t>
+          <t>28929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63927</t>
+          <t>49817</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>108815</t>
+          <t>88617</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82769</t>
+          <t>72225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162673</t>
+          <t>106009</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9227</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4444</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3631</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8521</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>13709</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21823</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3644</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9302</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2259</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3563</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>893</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8384</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170987</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170987</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170987</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172186</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172186</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172186</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>362</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>314733</t>
+          <t>296969</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>314733</t>
+          <t>296969</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>314733</t>
+          <t>296969</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>173717</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>158483</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>190640</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>58,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>119971</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>77142</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>142857</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>57,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>67,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>177968</t>
+          <t>125611</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160102</t>
+          <t>112461</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196191</t>
+          <t>137135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>297939</t>
+          <t>299328</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>244150</t>
+          <t>278565</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>323177</t>
+          <t>319241</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>78774</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>62124</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>94734</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,05%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>82942</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>59446</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128532</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>63767</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>52548</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92616</t>
+          <t>76563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>159642</t>
+          <t>142542</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>131933</t>
+          <t>124656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>215864</t>
+          <t>162755</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11247</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5942</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>19873</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>6678</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3019</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13389</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2423,107 +2423,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4234</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3660</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4252</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3755</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4580</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9660</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2735</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>4557</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>10860</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>271551</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>271551</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>271551</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>576</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
